--- a/output/roomself_excel/5859.xlsx
+++ b/output/roomself_excel/5859.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>333596</v>
+        <v>73200</v>
       </c>
       <c r="D2" t="n">
-        <v>8196</v>
+        <v>2176</v>
       </c>
       <c r="E2" t="n">
-        <v>802</v>
+        <v>322</v>
       </c>
       <c r="F2" t="n">
-        <v>633</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>219452</v>
+        <v>74562</v>
       </c>
       <c r="D3" t="n">
-        <v>5616</v>
+        <v>2188</v>
       </c>
       <c r="E3" t="n">
-        <v>685</v>
+        <v>311</v>
       </c>
       <c r="F3" t="n">
-        <v>598</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>254873</v>
+        <v>219452</v>
       </c>
       <c r="D4" t="n">
-        <v>6371</v>
+        <v>5616</v>
       </c>
       <c r="E4" t="n">
-        <v>651</v>
+        <v>685</v>
       </c>
       <c r="F4" t="n">
-        <v>636</v>
+        <v>598</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>51870</v>
+        <v>93046</v>
       </c>
       <c r="D5" t="n">
-        <v>1852</v>
+        <v>2644</v>
       </c>
       <c r="E5" t="n">
-        <v>318</v>
+        <v>365</v>
       </c>
       <c r="F5" t="n">
-        <v>214</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13876</v>
+        <v>107440</v>
       </c>
       <c r="D6" t="n">
-        <v>1040</v>
+        <v>2668</v>
       </c>
       <c r="E6" t="n">
-        <v>283</v>
+        <v>417</v>
       </c>
       <c r="F6" t="n">
-        <v>102</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>93046</v>
+        <v>13876</v>
       </c>
       <c r="D7" t="n">
-        <v>2644</v>
+        <v>1040</v>
       </c>
       <c r="E7" t="n">
-        <v>365</v>
+        <v>102</v>
       </c>
       <c r="F7" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -598,14 +598,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>34532</v>
+        <v>30960</v>
       </c>
       <c r="D8" t="n">
-        <v>1488</v>
+        <v>1408</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30960</v>
+        <v>55275</v>
       </c>
       <c r="D9" t="n">
-        <v>1408</v>
+        <v>1904</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>55275</v>
+        <v>22806</v>
       </c>
       <c r="D10" t="n">
-        <v>1904</v>
+        <v>1228</v>
       </c>
       <c r="E10" t="n">
-        <v>436</v>
+        <v>203</v>
       </c>
       <c r="F10" t="n">
-        <v>313</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>44825</v>
+        <v>51870</v>
       </c>
       <c r="D11" t="n">
-        <v>1752</v>
+        <v>1852</v>
       </c>
       <c r="E11" t="n">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="F11" t="n">
-        <v>187</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>107440</v>
+        <v>254873</v>
       </c>
       <c r="D12" t="n">
-        <v>2668</v>
+        <v>6371</v>
       </c>
       <c r="E12" t="n">
-        <v>633</v>
+        <v>651</v>
       </c>
       <c r="F12" t="n">
-        <v>315</v>
+        <v>636</v>
       </c>
     </row>
     <row r="13">
@@ -712,16 +712,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>50042</v>
+        <v>185834</v>
       </c>
       <c r="D13" t="n">
-        <v>1812</v>
+        <v>5964</v>
       </c>
       <c r="E13" t="n">
-        <v>309</v>
+        <v>633</v>
       </c>
       <c r="F13" t="n">
-        <v>222</v>
+        <v>498</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,64 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22806</v>
+        <v>34532</v>
       </c>
       <c r="D14" t="n">
-        <v>1228</v>
+        <v>1488</v>
       </c>
       <c r="E14" t="n">
-        <v>203</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>169</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>44825</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1752</v>
+      </c>
+      <c r="E15" t="n">
+        <v>313</v>
+      </c>
+      <c r="F15" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>50042</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1812</v>
+      </c>
+      <c r="E16" t="n">
+        <v>309</v>
+      </c>
+      <c r="F16" t="n">
+        <v>222</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/5859.xlsx
+++ b/output/roomself_excel/5859.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,62 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
         </is>
       </c>
     </row>
@@ -475,12 +525,34 @@
       <c r="D2" t="n">
         <v>2176</v>
       </c>
-      <c r="E2" t="n">
-        <v>322</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>290</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="G2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>244</v>
+      </c>
+      <c r="J2" t="n">
+        <v>22</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +569,34 @@
       <c r="D3" t="n">
         <v>2188</v>
       </c>
-      <c r="E3" t="n">
-        <v>311</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>304</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="G3" t="n">
+        <v>46</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>258</v>
+      </c>
+      <c r="J3" t="n">
+        <v>22</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,11 +613,49 @@
       <c r="D4" t="n">
         <v>5616</v>
       </c>
-      <c r="E4" t="n">
-        <v>685</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>598</v>
+        <v>572</v>
+      </c>
+      <c r="G4" t="n">
+        <v>47</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>597</v>
+      </c>
+      <c r="J4" t="n">
+        <v>26</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>288</v>
+      </c>
+      <c r="M4" t="n">
+        <v>31</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>194</v>
+      </c>
+      <c r="P4" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="5">
@@ -541,12 +673,34 @@
       <c r="D5" t="n">
         <v>2644</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>296</v>
+      </c>
+      <c r="G5" t="n">
+        <v>31</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>365</v>
       </c>
-      <c r="F5" t="n">
+      <c r="J5" t="n">
         <v>41</v>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +717,34 @@
       <c r="D6" t="n">
         <v>2668</v>
       </c>
-      <c r="E6" t="n">
-        <v>417</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>315</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="G6" t="n">
+        <v>22</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>395</v>
+      </c>
+      <c r="J6" t="n">
+        <v>43</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +761,18 @@
       <c r="D7" t="n">
         <v>1040</v>
       </c>
-      <c r="E7" t="n">
-        <v>102</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +789,18 @@
       <c r="D8" t="n">
         <v>1408</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +817,26 @@
       <c r="D9" t="n">
         <v>1904</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>201</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>38</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +853,34 @@
       <c r="D10" t="n">
         <v>1228</v>
       </c>
-      <c r="E10" t="n">
-        <v>203</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>169</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="G10" t="n">
+        <v>22</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>181</v>
+      </c>
+      <c r="J10" t="n">
+        <v>43</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +897,34 @@
       <c r="D11" t="n">
         <v>1852</v>
       </c>
-      <c r="E11" t="n">
-        <v>318</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>214</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="G11" t="n">
+        <v>45</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>273</v>
+      </c>
+      <c r="J11" t="n">
+        <v>24</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +941,42 @@
       <c r="D12" t="n">
         <v>6371</v>
       </c>
-      <c r="E12" t="n">
-        <v>651</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>636</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="G12" t="n">
+        <v>45</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>606</v>
+      </c>
+      <c r="J12" t="n">
+        <v>25</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>265</v>
+      </c>
+      <c r="M12" t="n">
+        <v>24</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +993,26 @@
       <c r="D13" t="n">
         <v>5964</v>
       </c>
-      <c r="E13" t="n">
-        <v>633</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>498</v>
-      </c>
+        <v>795</v>
+      </c>
+      <c r="G13" t="n">
+        <v>22</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +1029,18 @@
       <c r="D14" t="n">
         <v>1488</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +1057,34 @@
       <c r="D15" t="n">
         <v>1752</v>
       </c>
-      <c r="E15" t="n">
-        <v>313</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>187</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="G15" t="n">
+        <v>24</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>163</v>
+      </c>
+      <c r="J15" t="n">
+        <v>38</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1101,34 @@
       <c r="D16" t="n">
         <v>1812</v>
       </c>
-      <c r="E16" t="n">
-        <v>309</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>222</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="G16" t="n">
+        <v>31</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>191</v>
+      </c>
+      <c r="J16" t="n">
+        <v>47</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/5859.xlsx
+++ b/output/roomself_excel/5859.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,46 @@
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ExtWallWidth_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
         </is>
       </c>
     </row>
@@ -553,6 +593,26 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>166</v>
+      </c>
+      <c r="T2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -597,6 +657,38 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>46</v>
+      </c>
+      <c r="T3" t="n">
+        <v>46</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>188</v>
+      </c>
+      <c r="X3" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -656,6 +748,38 @@
       </c>
       <c r="P4" t="n">
         <v>41</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>370</v>
+      </c>
+      <c r="T4" t="n">
+        <v>47</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>79</v>
+      </c>
+      <c r="X4" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="5">
@@ -701,6 +825,26 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>185</v>
+      </c>
+      <c r="T5" t="n">
+        <v>41</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -745,6 +889,26 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>187</v>
+      </c>
+      <c r="T6" t="n">
+        <v>43</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -773,6 +937,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -801,6 +973,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -837,6 +1017,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -881,6 +1069,26 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>93</v>
+      </c>
+      <c r="T10" t="n">
+        <v>43</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -925,6 +1133,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -977,6 +1193,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1013,6 +1237,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1041,6 +1273,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1085,6 +1325,26 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>82</v>
+      </c>
+      <c r="T15" t="n">
+        <v>38</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1129,6 +1389,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
